--- a/BDD_normalized_format/espagne_normalisee.xlsx
+++ b/BDD_normalized_format/espagne_normalisee.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,10 +456,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>taille_colis</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fragile</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>poids_kg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>prix_livraison_eur</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>statut_colis</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>satisfaction_normalisee</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>commentaire_global</t>
         </is>
@@ -491,10 +516,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,10 +568,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,10 +620,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,10 +672,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,10 +724,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -646,10 +776,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -677,10 +828,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -708,10 +880,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -739,10 +932,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,10 +984,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -801,10 +1036,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -832,10 +1088,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -863,10 +1140,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -894,10 +1192,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="I15" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -925,10 +1244,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -956,10 +1296,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -987,10 +1348,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1018,10 +1400,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="I19" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1049,10 +1452,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1080,10 +1504,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I21" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1111,10 +1556,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1142,10 +1608,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1173,10 +1660,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1204,10 +1712,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1235,10 +1764,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>5</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1266,10 +1816,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1297,10 +1868,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1328,10 +1920,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1359,10 +1972,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>5</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1390,10 +2024,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I31" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1421,10 +2076,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1452,10 +2128,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="I33" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1483,10 +2180,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I34" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1514,10 +2232,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>3</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1545,10 +2284,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I36" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1576,10 +2336,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="I37" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1607,10 +2388,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>5</v>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1638,10 +2440,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1669,10 +2492,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I40" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1700,10 +2544,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I41" t="n">
+        <v>23.7925</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1731,10 +2596,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I42" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1762,10 +2648,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1793,10 +2700,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1824,10 +2752,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>3</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="I45" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1855,10 +2804,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I46" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1886,10 +2856,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1917,10 +2908,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="I48" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1948,10 +2960,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I49" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1979,10 +3012,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>3</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="I50" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2010,10 +3064,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2041,10 +3116,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>3</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2072,10 +3168,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I53" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2103,10 +3220,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I54" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2134,10 +3272,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="I55" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2165,10 +3324,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2196,10 +3376,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I57" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>3</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2227,10 +3428,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>5</v>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2258,10 +3480,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>3</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>3</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2289,10 +3532,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
         <v>5</v>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2320,10 +3584,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="I61" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2351,10 +3636,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="I62" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>5</v>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2382,10 +3688,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>3</v>
-      </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2413,10 +3740,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>3</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I64" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2444,10 +3792,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>3</v>
-      </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I65" t="n">
+        <v>23.7925</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2475,10 +3844,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>3</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I66" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2506,10 +3896,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
         <v>5</v>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2537,10 +3948,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I68" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>3</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2568,10 +4000,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>3</v>
-      </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I69" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2599,10 +4052,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="I70" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2630,10 +4104,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>3</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I71" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2661,10 +4156,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>3</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I72" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2692,10 +4208,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>3</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="I73" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2723,10 +4260,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>3</v>
-      </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I74" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2754,10 +4312,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I75" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2785,10 +4364,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I76" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2816,10 +4416,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I77" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2847,10 +4468,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I78" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2878,10 +4520,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I79" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>3</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2909,10 +4572,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I80" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
         <v>5</v>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2940,10 +4624,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>3</v>
-      </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="I81" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2971,10 +4676,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="I82" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
         <v>5</v>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3002,10 +4728,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>3</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="I83" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>3</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3033,10 +4780,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>3</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I84" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>3</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3064,10 +4832,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>3</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>3</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3095,10 +4884,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>3</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I86" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>3</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3126,10 +4936,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>3</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I87" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3157,10 +4988,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
         <v>5</v>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3188,10 +5040,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I89" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
         <v>1</v>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3219,10 +5092,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>3</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="I90" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>3</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3250,10 +5144,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="I91" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
         <v>5</v>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3281,10 +5196,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>3</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I92" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3312,10 +5248,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="I93" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
         <v>5</v>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3343,10 +5300,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>3</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="I94" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>3</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3374,10 +5352,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>3</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I95" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>3</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3405,10 +5404,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I96" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
         <v>1</v>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3436,10 +5456,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I97" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
         <v>5</v>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3467,10 +5508,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>3</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I98" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>3</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3498,10 +5560,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I99" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
         <v>5</v>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3529,10 +5612,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="I100" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
         <v>5</v>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3560,10 +5664,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I101" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
         <v>5</v>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3591,10 +5716,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F102" t="n">
-        <v>3</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I102" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3622,10 +5768,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="I103" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
         <v>1</v>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3653,10 +5820,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="I104" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
         <v>5</v>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3684,10 +5872,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I105" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
         <v>5</v>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3715,10 +5924,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>3</v>
-      </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I106" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>3</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3746,10 +5976,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F107" t="n">
-        <v>3</v>
-      </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I107" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3777,10 +6028,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F108" t="n">
-        <v>3</v>
-      </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="I108" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>3</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3808,10 +6080,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F109" t="n">
-        <v>3</v>
-      </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I109" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>3</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3839,10 +6132,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I110" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
         <v>5</v>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3870,10 +6184,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F111" t="n">
-        <v>3</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I111" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>3</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3901,10 +6236,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F112" t="n">
-        <v>3</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I112" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>3</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3932,10 +6288,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F113" t="n">
-        <v>3</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I113" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3963,10 +6340,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I114" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
         <v>5</v>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3994,10 +6392,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F115" t="n">
-        <v>3</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I115" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>3</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4025,10 +6444,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I116" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
         <v>5</v>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4056,10 +6496,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F117" t="n">
-        <v>3</v>
-      </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I117" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>3</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4087,10 +6548,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F118" t="n">
-        <v>3</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I118" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>3</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4118,10 +6600,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F119" t="n">
-        <v>3</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="I119" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>3</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4149,10 +6652,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F120" t="n">
-        <v>3</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I120" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>3</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4180,10 +6704,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F121" t="n">
-        <v>3</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I121" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>3</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4211,10 +6756,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="I122" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
         <v>5</v>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4242,10 +6808,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F123" t="n">
-        <v>3</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="I123" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>3</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4273,10 +6860,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F124" t="n">
-        <v>3</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4304,10 +6912,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I125" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
         <v>5</v>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4335,10 +6964,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F126" t="n">
-        <v>3</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="I126" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>3</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4366,10 +7016,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F127" t="n">
-        <v>3</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>3</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4397,10 +7068,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>3</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I128" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>3</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4428,10 +7120,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>3</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I129" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>3</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4459,10 +7172,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F130" t="n">
-        <v>3</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>3</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4490,10 +7224,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F131" t="n">
-        <v>3</v>
-      </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I131" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4521,10 +7276,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F132" t="n">
-        <v>3</v>
-      </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I132" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>3</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4552,10 +7328,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F133" t="n">
-        <v>3</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>3</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4583,10 +7380,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F134" t="n">
-        <v>3</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I134" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>3</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4614,10 +7432,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F135" t="n">
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="I135" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
         <v>5</v>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4645,10 +7484,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F136" t="n">
-        <v>3</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I136" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4676,10 +7536,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F137" t="n">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I137" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
         <v>5</v>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4707,10 +7588,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F138" t="n">
-        <v>3</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I138" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>3</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4738,10 +7640,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F139" t="n">
-        <v>3</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I139" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>3</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4769,10 +7692,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>3</v>
-      </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I140" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>3</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4800,10 +7744,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F141" t="n">
-        <v>3</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I141" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>3</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4831,10 +7796,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F142" t="n">
-        <v>3</v>
-      </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I142" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>3</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4862,10 +7848,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F143" t="n">
-        <v>3</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I143" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>3</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4893,10 +7900,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F144" t="n">
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="I144" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
         <v>5</v>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4924,10 +7952,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F145" t="n">
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I145" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
         <v>5</v>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4955,10 +8004,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F146" t="n">
-        <v>3</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I146" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>3</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4986,10 +8056,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F147" t="n">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I147" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
         <v>1</v>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5017,10 +8108,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F148" t="n">
-        <v>3</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I148" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>3</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5048,10 +8160,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F149" t="n">
-        <v>3</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I149" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>3</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5079,10 +8212,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>3</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I150" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>3</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5110,10 +8264,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I151" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
         <v>5</v>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5141,10 +8316,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I152" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
         <v>5</v>
       </c>
-      <c r="G152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5172,10 +8368,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I153" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
         <v>5</v>
       </c>
-      <c r="G153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5203,10 +8420,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="I154" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
         <v>5</v>
       </c>
-      <c r="G154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5234,10 +8472,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F155" t="n">
-        <v>3</v>
-      </c>
-      <c r="G155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I155" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K155" t="n">
+        <v>3</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5265,10 +8524,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F156" t="n">
-        <v>3</v>
-      </c>
-      <c r="G156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I156" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K156" t="n">
+        <v>3</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5296,10 +8576,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F157" t="n">
-        <v>3</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="I157" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K157" t="n">
+        <v>3</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5327,10 +8628,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="I158" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K158" t="n">
         <v>1</v>
       </c>
-      <c r="G158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5358,10 +8680,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I159" t="n">
+        <v>23.7925</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
         <v>5</v>
       </c>
-      <c r="G159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5389,10 +8732,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F160" t="n">
-        <v>3</v>
-      </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I160" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>3</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5420,10 +8784,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F161" t="n">
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I161" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
         <v>5</v>
       </c>
-      <c r="G161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5451,10 +8836,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F162" t="n">
-        <v>3</v>
-      </c>
-      <c r="G162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I162" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>3</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5482,10 +8888,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F163" t="n">
-        <v>3</v>
-      </c>
-      <c r="G163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I163" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>3</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5513,10 +8940,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F164" t="n">
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I164" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
         <v>5</v>
       </c>
-      <c r="G164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5544,10 +8992,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F165" t="n">
-        <v>3</v>
-      </c>
-      <c r="G165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I165" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K165" t="n">
+        <v>3</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5575,10 +9044,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F166" t="n">
-        <v>3</v>
-      </c>
-      <c r="G166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I166" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>3</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5606,10 +9096,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F167" t="n">
-        <v>3</v>
-      </c>
-      <c r="G167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I167" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>3</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5637,10 +9148,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F168" t="n">
-        <v>3</v>
-      </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I168" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>3</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5668,10 +9200,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F169" t="n">
-        <v>3</v>
-      </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K169" t="n">
+        <v>3</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5699,10 +9252,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F170" t="n">
-        <v>3</v>
-      </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="I170" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>3</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5730,10 +9304,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F171" t="n">
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K171" t="n">
         <v>5</v>
       </c>
-      <c r="G171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5761,10 +9356,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F172" t="n">
-        <v>3</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I172" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>3</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5792,10 +9408,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F173" t="n">
-        <v>3</v>
-      </c>
-      <c r="G173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I173" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>3</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5823,10 +9460,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F174" t="n">
-        <v>3</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I174" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K174" t="n">
+        <v>3</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5854,10 +9512,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F175" t="n">
-        <v>3</v>
-      </c>
-      <c r="G175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K175" t="n">
+        <v>3</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5885,10 +9564,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F176" t="n">
-        <v>3</v>
-      </c>
-      <c r="G176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I176" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>3</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5916,10 +9616,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F177" t="n">
-        <v>3</v>
-      </c>
-      <c r="G177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="I177" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K177" t="n">
+        <v>3</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5947,10 +9668,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F178" t="n">
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I178" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K178" t="n">
         <v>5</v>
       </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5978,10 +9720,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F179" t="n">
-        <v>3</v>
-      </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I179" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>3</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6009,10 +9772,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F180" t="n">
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="I180" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
         <v>5</v>
       </c>
-      <c r="G180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6040,10 +9824,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F181" t="n">
-        <v>3</v>
-      </c>
-      <c r="G181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I181" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K181" t="n">
+        <v>3</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6071,10 +9876,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F182" t="n">
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I182" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K182" t="n">
         <v>5</v>
       </c>
-      <c r="G182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6102,10 +9928,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F183" t="n">
-        <v>3</v>
-      </c>
-      <c r="G183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>11.5275</v>
+      </c>
+      <c r="I183" t="n">
+        <v>23.7925</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K183" t="n">
+        <v>3</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6133,10 +9980,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F184" t="n">
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="I184" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K184" t="n">
         <v>5</v>
       </c>
-      <c r="G184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6164,10 +10032,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F185" t="n">
-        <v>3</v>
-      </c>
-      <c r="G185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I185" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K185" t="n">
+        <v>3</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6195,10 +10084,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F186" t="n">
-        <v>3</v>
-      </c>
-      <c r="G186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I186" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K186" t="n">
+        <v>3</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6226,10 +10136,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F187" t="n">
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="I187" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
         <v>5</v>
       </c>
-      <c r="G187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6257,10 +10188,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F188" t="n">
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I188" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
         <v>5</v>
       </c>
-      <c r="G188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6288,10 +10240,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F189" t="n">
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I189" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K189" t="n">
         <v>1</v>
       </c>
-      <c r="G189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6319,10 +10292,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F190" t="n">
-        <v>3</v>
-      </c>
-      <c r="G190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="I190" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K190" t="n">
+        <v>3</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6350,10 +10344,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F191" t="n">
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I191" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="K191" t="n">
         <v>5</v>
       </c>
-      <c r="G191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6381,10 +10396,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F192" t="n">
-        <v>3</v>
-      </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="I192" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>3</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6412,10 +10448,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F193" t="n">
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I193" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
         <v>1</v>
       </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6443,10 +10500,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F194" t="n">
-        <v>3</v>
-      </c>
-      <c r="G194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="I194" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Retardé</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>3</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6474,10 +10552,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F195" t="n">
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="I195" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
         <v>5</v>
       </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6505,10 +10604,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F196" t="n">
-        <v>3</v>
-      </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I196" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>3</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6536,10 +10656,31 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="F197" t="n">
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I197" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
         <v>5</v>
       </c>
-      <c r="G197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6567,10 +10708,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F198" t="n">
-        <v>3</v>
-      </c>
-      <c r="G198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I198" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K198" t="n">
+        <v>3</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6598,10 +10760,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F199" t="n">
-        <v>3</v>
-      </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="I199" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K199" t="n">
+        <v>3</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6629,10 +10812,31 @@
           <t>EXPRESS</t>
         </is>
       </c>
-      <c r="F200" t="n">
-        <v>3</v>
-      </c>
-      <c r="G200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I200" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Livré</t>
+        </is>
+      </c>
+      <c r="K200" t="n">
+        <v>3</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6660,10 +10864,31 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="F201" t="n">
-        <v>3</v>
-      </c>
-      <c r="G201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Petit</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>En transit</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>3</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
